--- a/On Air Progress Tracker.xlsx
+++ b/On Air Progress Tracker.xlsx
@@ -4,19 +4,53 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23256" windowHeight="13896" activeTab="1"/>
+    <workbookView windowWidth="23256" windowHeight="13896" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="4" r:id="rId1"/>
     <sheet name="Ha Noi Progress Tracker" sheetId="1" r:id="rId2"/>
     <sheet name="North Progress Tracker" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="6" r:id="rId4"/>
+    <sheet name="WpsReserved_CellImgList" sheetId="5" state="veryHidden" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Ha Noi Progress Tracker'!$A$3:$AE$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'North Progress Tracker'!$A$2:$T$17</definedName>
+  </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
+<file path=xl/cellimages.xml><?xml version="1.0" encoding="utf-8"?>
+<etc:cellImages xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="ID_DD0E3DAA24804B74A77E3893CB6FEE3A" descr="upload_post_object_v2_746142189"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="617220" cy="160020"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+</etc:cellImages>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="130">
   <si>
     <t>Ha Noi</t>
   </si>
@@ -42,6 +76,24 @@
     <t>Hai Phong</t>
   </si>
   <si>
+    <t>Hai Duong</t>
+  </si>
+  <si>
+    <t>Hung Yen</t>
+  </si>
+  <si>
+    <t>Thai Binh</t>
+  </si>
+  <si>
+    <t>Thai Nguyen</t>
+  </si>
+  <si>
+    <t>Ninh Binh</t>
+  </si>
+  <si>
+    <t>Monitor</t>
+  </si>
+  <si>
     <t>No</t>
   </si>
   <si>
@@ -51,6 +103,12 @@
     <t>Site Name</t>
   </si>
   <si>
+    <t>OM Link Status</t>
+  </si>
+  <si>
+    <t>Pre Swap Scripts</t>
+  </si>
+  <si>
     <t>Site Status</t>
   </si>
   <si>
@@ -63,21 +121,75 @@
     <t>On-air Time</t>
   </si>
   <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Post Swap Scripts</t>
+  </si>
+  <si>
+    <t>NSN-&gt;HW Neighbors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CQT Start Time </t>
+  </si>
+  <si>
+    <t>CQT Complete Time</t>
+  </si>
+  <si>
     <t>Remark</t>
   </si>
   <si>
+    <t>NEName_New4G</t>
+  </si>
+  <si>
+    <t>NEName_New5G</t>
+  </si>
+  <si>
+    <t>NEname_Old_4G_NSN</t>
+  </si>
+  <si>
+    <t>batch</t>
+  </si>
+  <si>
+    <t>Vendor</t>
+  </si>
+  <si>
+    <t>Alarm（update on May 18 15:00)</t>
+  </si>
+  <si>
     <t>Pilot</t>
   </si>
   <si>
     <t>HN_GLM_CN_NINH_HIEP</t>
   </si>
   <si>
+    <t>Connected</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
     <t>On Air</t>
   </si>
   <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>Not Yet</t>
+  </si>
+  <si>
     <t>4G Swap+New 5G Building 2.6G</t>
   </si>
   <si>
+    <t>HNIPDG02</t>
+  </si>
+  <si>
+    <t>batch1</t>
+  </si>
+  <si>
+    <t>NSN</t>
+  </si>
+  <si>
     <t>HN_GLM_CN_NINH_HIEP_CRAN_2</t>
   </si>
   <si>
@@ -87,67 +199,293 @@
     <t>4G Swap</t>
   </si>
   <si>
+    <t>HNIPDG03</t>
+  </si>
+  <si>
+    <t>batch2</t>
+  </si>
+  <si>
     <t>HN_GLM_NINH_HIEP_2_CRAN</t>
   </si>
   <si>
+    <t>HNIPDG14</t>
+  </si>
+  <si>
+    <t>HN_GLM_NINH_HIEP</t>
+  </si>
+  <si>
+    <t>HN_GLM_CAU_DUONG</t>
+  </si>
+  <si>
+    <t>Swap 4G + Newbuild 5G Single 2.6 32T</t>
+  </si>
+  <si>
+    <t>HNIPDG01</t>
+  </si>
+  <si>
+    <t>batch3</t>
+  </si>
+  <si>
+    <t>45G,Certificate Invalid,45G,User Plane Fault,45G,IP Clock Link Failure</t>
+  </si>
+  <si>
+    <t>HN_GLM_CONG_THON</t>
+  </si>
+  <si>
+    <t>2 sectors OK, 1 is NOK due to CPRI issue</t>
+  </si>
+  <si>
+    <t>HNIPDG04</t>
+  </si>
+  <si>
+    <t>45G,Certificate Invalid,45G,User Plane Fault,5G,BBU CPRI Interface Error,5G,RF Unit Maintenance Link Failure</t>
+  </si>
+  <si>
+    <t>HN_GLM_DINH_XUYEN_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2026/5/15 17:00</t>
+  </si>
+  <si>
+    <t>HNIPDG06</t>
+  </si>
+  <si>
+    <t>HN_GLM_DINH_XUYEN_3</t>
+  </si>
+  <si>
+    <t>HNIPDG07</t>
+  </si>
+  <si>
+    <t>45G,Certificate Invalid,45G,Transmission Optical Interface Error,5G,BBU CPRI Interface Error,5G,RF Unit Maintenance Link Failure</t>
+  </si>
+  <si>
+    <t>HN_GLM_DUONG_HA</t>
+  </si>
+  <si>
+    <t>2026/5/15 22:24:00 sector C issue</t>
+  </si>
+  <si>
+    <t>HNIPDG08</t>
+  </si>
+  <si>
+    <t>4G,BBU CPRI Interface Error,4G,Cell Blocked,4G,Data Configuration Exceeding Licensed Limit,4G,RF Unit Maintenance Link Failure,5G,BBU CPRI Interface Error,5G,RF Unit Maintenance Link Failure</t>
+  </si>
+  <si>
+    <t>HN_GLM_DUONG_HA_2</t>
+  </si>
+  <si>
+    <t>NOK due to CPRI issue</t>
+  </si>
+  <si>
+    <t>HNIPDG09</t>
+  </si>
+  <si>
+    <t>45G,User Plane Fault,5G,BBU CPRI Interface Error,5G,RF Unit Maintenance Link Failure</t>
+  </si>
+  <si>
+    <t>HN_GLM_HA_HUY_TAP</t>
+  </si>
+  <si>
+    <t>2026/5/15 22:10:00. 4G sector C locked</t>
+  </si>
+  <si>
+    <t>HNIPDG10</t>
+  </si>
+  <si>
+    <t>HN_GLM_YEN_THUONG_CRAN</t>
+  </si>
+  <si>
+    <t>HN_GLM_LA_COI</t>
+  </si>
+  <si>
+    <t>HNIPDG11</t>
+  </si>
+  <si>
+    <t>45G,Certificate Invalid,45G,User Plane Fault</t>
+  </si>
+  <si>
+    <t>HN_GLM_NGA_4_NINH_HIEP</t>
+  </si>
+  <si>
+    <t>HNIPDG12</t>
+  </si>
+  <si>
+    <t>HNIPDG13</t>
+  </si>
+  <si>
+    <t>HN_GLM_XUAN_DUC</t>
+  </si>
+  <si>
+    <t>NOK due to CRPI issue</t>
+  </si>
+  <si>
+    <t>2026/5/15 22:00:00 No 5G</t>
+  </si>
+  <si>
+    <t>HNIPDG21</t>
+  </si>
+  <si>
+    <t>45G,Transmission Optical Interface Error,45G,User Plane Fault</t>
+  </si>
+  <si>
+    <t>HN_GLM_YEN_THUONG</t>
+  </si>
+  <si>
+    <t>2026/5/15 21:50:00 Cannot camp on 5G</t>
+  </si>
+  <si>
+    <t>HNIPDG22</t>
+  </si>
+  <si>
+    <t>5G,BBU CPRI Interface Error,5G,gNodeB Out of Service,5G,NR DU Cell TRP Unavailable,5G,RF Unit DC Input Power Failure,5G,RF Unit External Power Supply Insufficient,5G,RF Unit Maintenance Link Failure</t>
+  </si>
+  <si>
+    <t>Swap 4G</t>
+  </si>
+  <si>
+    <t>3.8G_N77</t>
+  </si>
+  <si>
+    <t>2.6G_N41</t>
+  </si>
+  <si>
+    <t>NEName_New</t>
+  </si>
+  <si>
+    <t>NEname_Old</t>
+  </si>
+  <si>
+    <t>Batch</t>
+  </si>
+  <si>
     <t>HPG_CHI_DONG_BAI</t>
   </si>
   <si>
     <t>Newbuild 5G Dual (2.6 64T + 3.8 64T)</t>
   </si>
   <si>
+    <t>HPGCHI02_5G</t>
+  </si>
+  <si>
+    <t>HPG_CHI_DONG_BAI_4G</t>
+  </si>
+  <si>
+    <t>HUA</t>
+  </si>
+  <si>
     <t>HPG_TNN_TT_HANH_CHINH_2_01R</t>
   </si>
   <si>
+    <t>HPGTNN57_5G</t>
+  </si>
+  <si>
+    <t>HPG_TNN_TT_HANH_CHINH_2_4G</t>
+  </si>
+  <si>
+    <t>5G,RF Unit DC Input Power Failure,5G,RF Unit Maintenance Link Failure</t>
+  </si>
+  <si>
     <t>HPG_CHI_CAT_BA_4</t>
   </si>
   <si>
     <t>Newbuild 5G Single 2.6 32T</t>
+  </si>
+  <si>
+    <t>HPGCHI07_5G</t>
+  </si>
+  <si>
+    <t>HPG_CHI_CAT_BA_4_4G</t>
+  </si>
+  <si>
+    <t>HDG_CGG_DUC_CHINH_3</t>
+  </si>
+  <si>
+    <t>HPGVHA10_5G</t>
+  </si>
+  <si>
+    <t>HDG_CGG_DUC_CHINH_3_4G</t>
+  </si>
+  <si>
+    <t>HYN_VLM_CHI_DAO_2</t>
+  </si>
+  <si>
+    <t>TNN_PBH_THUONG_DINH_2</t>
+  </si>
+  <si>
+    <t>HDG_CGG_CAM_DINH</t>
+  </si>
+  <si>
+    <t>HDG_CGG_CAM_GIANG_2</t>
+  </si>
+  <si>
+    <t>HDG_CGG_CAM_PHUC</t>
+  </si>
+  <si>
+    <t>HDG_CGG_CAM_VU</t>
+  </si>
+  <si>
+    <t>HDG_CGG_CAO_AN</t>
+  </si>
+  <si>
+    <t>HDG_CGG_CAO_AN_2</t>
+  </si>
+  <si>
+    <t>HYN_YMY_LIEU_XA_3</t>
+  </si>
+  <si>
+    <t>TBH_DHG_DONG_XUAN</t>
+  </si>
+  <si>
+    <t>NB_GVN_GIA_SINH_2</t>
+  </si>
+  <si>
+    <t>NBHTHL03_5G</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="36">
+  <numFmts count="37">
     <numFmt numFmtId="176" formatCode="[DBNum1][$-804]yyyy&quot;年&quot;m&quot;月&quot;"/>
     <numFmt numFmtId="6" formatCode="&quot;￥&quot;#,##0;[Red]&quot;￥&quot;\-#,##0"/>
+    <numFmt numFmtId="177" formatCode="#\ ??/??"/>
+    <numFmt numFmtId="24" formatCode="\$#,##0_);[Red]\(\$#,##0\)"/>
+    <numFmt numFmtId="7" formatCode="&quot;￥&quot;#,##0.00;&quot;￥&quot;\-#,##0.00"/>
+    <numFmt numFmtId="178" formatCode="yy/m/d"/>
+    <numFmt numFmtId="179" formatCode="#\ ?/?"/>
+    <numFmt numFmtId="25" formatCode="\$#,##0.00_);\(\$#,##0.00\)"/>
+    <numFmt numFmtId="180" formatCode="mmmmm"/>
+    <numFmt numFmtId="181" formatCode="h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="182" formatCode="[DBNum1]上午/下午h&quot;时&quot;mm&quot;分&quot;"/>
+    <numFmt numFmtId="183" formatCode="[DBNum1][$-804]m&quot;月&quot;d&quot;日&quot;"/>
+    <numFmt numFmtId="184" formatCode="yyyy/m/d\ h:mm\ AM/PM"/>
+    <numFmt numFmtId="185" formatCode="mm/dd/yy"/>
+    <numFmt numFmtId="186" formatCode="m/d"/>
+    <numFmt numFmtId="187" formatCode="dd\-mmm\-yy"/>
+    <numFmt numFmtId="26" formatCode="\$#,##0.00_);[Red]\(\$#,##0.00\)"/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="8" formatCode="&quot;￥&quot;#,##0.00;[Red]&quot;￥&quot;\-#,##0.00"/>
+    <numFmt numFmtId="188" formatCode="h:mm\ AM/PM"/>
+    <numFmt numFmtId="189" formatCode="#\ ??"/>
+    <numFmt numFmtId="190" formatCode="[DBNum1]h&quot;时&quot;mm&quot;分&quot;"/>
+    <numFmt numFmtId="191" formatCode="mmmmm\-yy"/>
+    <numFmt numFmtId="192" formatCode="\¥#,##0;\¥\-#,##0"/>
     <numFmt numFmtId="23" formatCode="\$#,##0_);\(\$#,##0\)"/>
-    <numFmt numFmtId="177" formatCode="#\ ??/??"/>
+    <numFmt numFmtId="193" formatCode="\¥#,##0;[Red]\¥\-#,##0"/>
     <numFmt numFmtId="5" formatCode="&quot;￥&quot;#,##0;&quot;￥&quot;\-#,##0"/>
-    <numFmt numFmtId="24" formatCode="\$#,##0_);[Red]\(\$#,##0\)"/>
-    <numFmt numFmtId="178" formatCode="mm/dd/yy"/>
-    <numFmt numFmtId="25" formatCode="\$#,##0.00_);\(\$#,##0.00\)"/>
-    <numFmt numFmtId="26" formatCode="\$#,##0.00_);[Red]\(\$#,##0.00\)"/>
-    <numFmt numFmtId="179" formatCode="mmmmm"/>
-    <numFmt numFmtId="180" formatCode="[$-804]aaa"/>
-    <numFmt numFmtId="7" formatCode="&quot;￥&quot;#,##0.00;&quot;￥&quot;\-#,##0.00"/>
+    <numFmt numFmtId="194" formatCode="[DBNum1][$-804]yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;"/>
+    <numFmt numFmtId="195" formatCode="[$-804]aaaa"/>
+    <numFmt numFmtId="196" formatCode="\¥#,##0.00;\¥\-#,##0.00"/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="181" formatCode="[DBNum1]上午/下午h&quot;时&quot;mm&quot;分&quot;"/>
-    <numFmt numFmtId="182" formatCode="[DBNum1][$-804]m&quot;月&quot;d&quot;日&quot;"/>
-    <numFmt numFmtId="8" formatCode="&quot;￥&quot;#,##0.00;[Red]&quot;￥&quot;\-#,##0.00"/>
-    <numFmt numFmtId="183" formatCode="#\ ?/?"/>
-    <numFmt numFmtId="184" formatCode="[$-804]aaaa"/>
-    <numFmt numFmtId="185" formatCode="\¥#,##0.00;[Red]\¥\-#,##0.00"/>
-    <numFmt numFmtId="186" formatCode="yyyy/m/d\ h:mm\ AM/PM"/>
+    <numFmt numFmtId="197" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="198" formatCode="\¥#,##0.00;[Red]\¥\-#,##0.00"/>
+    <numFmt numFmtId="199" formatCode="mmmm\-yy"/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="187" formatCode="yy/m/d"/>
-    <numFmt numFmtId="188" formatCode="mmmmm\-yy"/>
-    <numFmt numFmtId="189" formatCode="[DBNum1][$-804]yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;"/>
-    <numFmt numFmtId="190" formatCode="\¥#,##0;\¥\-#,##0"/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="191" formatCode="mmmm\-yy"/>
-    <numFmt numFmtId="192" formatCode="#\ ??"/>
-    <numFmt numFmtId="193" formatCode="\¥#,##0;[Red]\¥\-#,##0"/>
-    <numFmt numFmtId="194" formatCode="\¥#,##0.00;\¥\-#,##0.00"/>
-    <numFmt numFmtId="195" formatCode="dd\-mmm\-yy"/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="196" formatCode="[DBNum1]h&quot;时&quot;mm&quot;分&quot;"/>
-    <numFmt numFmtId="197" formatCode="m/d"/>
-    <numFmt numFmtId="198" formatCode="h:mm:ss\ AM/PM"/>
-    <numFmt numFmtId="199" formatCode="h:mm\ AM/PM"/>
+    <numFmt numFmtId="200" formatCode="[$-804]aaa"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -169,14 +507,39 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10.5"/>
-      <color theme="1"/>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -185,13 +548,6 @@
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
@@ -210,17 +566,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color theme="0"/>
       <name val="等线"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF9C0006"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -234,11 +588,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="3"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -250,75 +604,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -340,14 +628,82 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="42">
+  <fills count="44">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -368,19 +724,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
+        <fgColor theme="8" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="-0.249977111117893"/>
+        <fgColor rgb="FFC5DEB5"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED7D31"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,18 +784,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -440,13 +796,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,49 +820,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,7 +844,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,7 +880,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,31 +904,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -578,13 +922,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -594,13 +932,56 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="14">
+  <borders count="23">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -615,6 +996,45 @@
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -635,9 +1055,7 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
+      <right/>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -660,6 +1078,63 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
@@ -673,11 +1148,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -721,36 +1202,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -770,263 +1221,522 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="41" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="38" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="15" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="197" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="22" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="22" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1094,6 +1804,26 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>617220</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>160020</xdr:rowOff>
+    </xdr:to>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1354,362 +2084,998 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:Q13"/>
+  <dimension ref="A2:X18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="9" style="2"/>
-    <col min="2" max="2" width="9" style="1"/>
-    <col min="3" max="4" width="7.6" style="27" customWidth="1"/>
-    <col min="5" max="5" width="9" style="28"/>
-    <col min="6" max="14" width="9" style="29"/>
-    <col min="15" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="9" style="3"/>
+    <col min="2" max="2" width="9" style="2"/>
+    <col min="3" max="4" width="7.6" style="114" customWidth="1"/>
+    <col min="5" max="5" width="9" style="115" hidden="1" customWidth="1"/>
+    <col min="6" max="14" width="9" style="116" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9" style="3" hidden="1" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:1">
-      <c r="A2" s="30" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" ht="25.5" spans="2:17">
-      <c r="B4" s="31" t="s">
+      <c r="A2" s="117" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" ht="25.5" spans="2:24">
+      <c r="B4" s="118" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="119" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="D4" s="120" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="43">
+      <c r="E4" s="130">
         <v>46141</v>
       </c>
-      <c r="F4" s="43">
+      <c r="F4" s="130">
         <f>E4+1</f>
         <v>46142</v>
       </c>
-      <c r="G4" s="43">
-        <f t="shared" ref="G4:Q4" si="0">F4+1</f>
+      <c r="G4" s="130">
+        <f t="shared" ref="G4:X4" si="0">F4+1</f>
         <v>46143</v>
       </c>
-      <c r="H4" s="43">
+      <c r="H4" s="130">
         <f t="shared" si="0"/>
         <v>46144</v>
       </c>
-      <c r="I4" s="43">
+      <c r="I4" s="130">
         <f t="shared" si="0"/>
         <v>46145</v>
       </c>
-      <c r="J4" s="43">
+      <c r="J4" s="130">
         <f t="shared" si="0"/>
         <v>46146</v>
       </c>
-      <c r="K4" s="43">
+      <c r="K4" s="130">
         <f t="shared" si="0"/>
         <v>46147</v>
       </c>
-      <c r="L4" s="43">
+      <c r="L4" s="130">
         <f t="shared" si="0"/>
         <v>46148</v>
       </c>
-      <c r="M4" s="43">
+      <c r="M4" s="130">
         <f t="shared" si="0"/>
         <v>46149</v>
       </c>
-      <c r="N4" s="43">
+      <c r="N4" s="130">
         <f t="shared" si="0"/>
         <v>46150</v>
       </c>
-      <c r="O4" s="43">
+      <c r="O4" s="130">
         <f t="shared" si="0"/>
         <v>46151</v>
       </c>
-      <c r="P4" s="43">
+      <c r="P4" s="130">
         <f t="shared" si="0"/>
         <v>46152</v>
       </c>
-      <c r="Q4" s="43">
+      <c r="Q4" s="130">
         <f t="shared" si="0"/>
         <v>46153</v>
       </c>
-    </row>
-    <row r="5" spans="2:17">
-      <c r="B5" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="35">
-        <f>COUNTIFS('Ha Noi Progress Tracker'!D:D,"&lt;&gt;",'Ha Noi Progress Tracker'!G:G,"&lt;&gt;",'Ha Noi Progress Tracker'!B:B,B5)</f>
+      <c r="R4" s="130">
+        <f t="shared" si="0"/>
+        <v>46154</v>
+      </c>
+      <c r="S4" s="130">
+        <f t="shared" si="0"/>
+        <v>46155</v>
+      </c>
+      <c r="T4" s="130">
+        <f t="shared" si="0"/>
+        <v>46156</v>
+      </c>
+      <c r="U4" s="130">
+        <f t="shared" si="0"/>
+        <v>46157</v>
+      </c>
+      <c r="V4" s="130">
+        <f t="shared" si="0"/>
+        <v>46158</v>
+      </c>
+      <c r="W4" s="130">
+        <f t="shared" si="0"/>
+        <v>46159</v>
+      </c>
+      <c r="X4" s="130">
+        <f t="shared" si="0"/>
+        <v>46160</v>
+      </c>
+    </row>
+    <row r="5" spans="2:24">
+      <c r="B5" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="122">
+        <f>COUNTIFS('Ha Noi Progress Tracker'!D:D,"&lt;&gt;",'Ha Noi Progress Tracker'!I:I,"&lt;&gt;",'Ha Noi Progress Tracker'!B:B,B5)</f>
+        <v>16</v>
+      </c>
+      <c r="D5" s="123" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="123">
+        <f>COUNTIFS('Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$I:$I,E4)</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="123">
+        <f>COUNTIFS('Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$I:$I,F4)</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="123">
+        <f>COUNTIFS('Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$I:$I,G4)</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="123">
+        <f>COUNTIFS('Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$I:$I,H4)</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="123">
+        <f>COUNTIFS('Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$I:$I,I4)</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="123">
+        <f>COUNTIFS('Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$I:$I,J4)</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="123">
+        <f>COUNTIFS('Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$I:$I,K4)</f>
+        <v>0</v>
+      </c>
+      <c r="L5" s="123">
+        <f>COUNTIFS('Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$I:$I,L4)</f>
+        <v>1</v>
+      </c>
+      <c r="M5" s="123">
+        <f>COUNTIFS('Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$I:$I,M4)</f>
+        <v>0</v>
+      </c>
+      <c r="N5" s="123">
+        <f>COUNTIFS('Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$I:$I,N4)</f>
+        <v>0</v>
+      </c>
+      <c r="O5" s="123">
+        <f>COUNTIFS('Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$I:$I,O4)</f>
+        <v>0</v>
+      </c>
+      <c r="P5" s="123">
+        <f>COUNTIFS('Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$I:$I,P4)</f>
+        <v>0</v>
+      </c>
+      <c r="Q5" s="123">
+        <f>COUNTIFS('Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$I:$I,Q4)</f>
+        <v>2</v>
+      </c>
+      <c r="R5" s="123">
+        <f>COUNTIFS('Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$I:$I,R4)</f>
+        <v>0</v>
+      </c>
+      <c r="S5" s="123">
+        <f>COUNTIFS('Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$I:$I,S4)</f>
+        <v>0</v>
+      </c>
+      <c r="T5" s="123">
+        <f>COUNTIFS('Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$I:$I,T4)</f>
+        <v>0</v>
+      </c>
+      <c r="U5" s="123">
+        <f>COUNTIFS('Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$I:$I,U4)</f>
+        <v>13</v>
+      </c>
+      <c r="V5" s="123">
+        <f>COUNTIFS('Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$I:$I,V4)</f>
+        <v>0</v>
+      </c>
+      <c r="W5" s="123">
+        <f>COUNTIFS('Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$I:$I,W4)</f>
+        <v>0</v>
+      </c>
+      <c r="X5" s="123">
+        <f>COUNTIFS('Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$I:$I,X4)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:24">
+      <c r="B6" s="124"/>
+      <c r="C6" s="125">
+        <f>SUMPRODUCT(--ISNUMBER('Ha Noi Progress Tracker'!M:M))</f>
+        <v>11</v>
+      </c>
+      <c r="D6" s="126" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="123">
+        <f>COUNTIFS('Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$M:$M,E4)</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="123">
+        <f>COUNTIFS('Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$M:$M,F4)</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="123">
+        <f>COUNTIFS('Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$M:$M,G4)</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="123">
+        <f>COUNTIFS('Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$M:$M,H4)</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="123">
+        <f>COUNTIFS('Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$M:$M,I4)</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="123">
+        <f>COUNTIFS('Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$M:$M,J4)</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="123">
+        <f>COUNTIFS('Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$M:$M,K4)</f>
+        <v>0</v>
+      </c>
+      <c r="L6" s="123">
+        <f>COUNTIFS('Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$M:$M,L4)</f>
+        <v>1</v>
+      </c>
+      <c r="M6" s="123">
+        <f>COUNTIFS('Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$M:$M,M4)</f>
+        <v>0</v>
+      </c>
+      <c r="N6" s="123">
+        <f>COUNTIFS('Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$M:$M,N4)</f>
+        <v>0</v>
+      </c>
+      <c r="O6" s="123">
+        <f>COUNTIFS('Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$M:$M,O4)</f>
+        <v>0</v>
+      </c>
+      <c r="P6" s="123">
+        <f>COUNTIFS('Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$M:$M,P4)</f>
+        <v>0</v>
+      </c>
+      <c r="Q6" s="123">
+        <f>COUNTIFS('Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$M:$M,Q4)</f>
+        <v>0</v>
+      </c>
+      <c r="R6" s="123">
+        <f>COUNTIFS('Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$M:$M,R4)</f>
+        <v>0</v>
+      </c>
+      <c r="S6" s="123">
+        <f>COUNTIFS('Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$M:$M,S4)</f>
+        <v>0</v>
+      </c>
+      <c r="T6" s="123">
+        <f>COUNTIFS('Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$M:$M,T4)</f>
+        <v>0</v>
+      </c>
+      <c r="U6" s="123">
+        <f>COUNTIFS('Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$M:$M,U4)</f>
+        <v>10</v>
+      </c>
+      <c r="V6" s="123">
+        <f>COUNTIFS('Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$M:$M,V4)</f>
+        <v>0</v>
+      </c>
+      <c r="W6" s="123">
+        <f>COUNTIFS('Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$M:$M,W4)</f>
+        <v>0</v>
+      </c>
+      <c r="X6" s="123">
+        <f>COUNTIFS('Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$M:$M,X4)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="15:24">
+      <c r="O7" s="116"/>
+      <c r="P7" s="116"/>
+      <c r="Q7" s="116"/>
+      <c r="R7" s="116"/>
+      <c r="S7" s="116"/>
+      <c r="T7" s="116"/>
+      <c r="U7" s="116"/>
+      <c r="V7" s="116"/>
+      <c r="W7" s="116"/>
+      <c r="X7" s="116"/>
+    </row>
+    <row r="8" spans="15:24">
+      <c r="O8" s="116"/>
+      <c r="P8" s="116"/>
+      <c r="Q8" s="116"/>
+      <c r="R8" s="116"/>
+      <c r="S8" s="116"/>
+      <c r="T8" s="116"/>
+      <c r="U8" s="116"/>
+      <c r="V8" s="116"/>
+      <c r="W8" s="116"/>
+      <c r="X8" s="116"/>
+    </row>
+    <row r="9" spans="15:24">
+      <c r="O9" s="116"/>
+      <c r="P9" s="116"/>
+      <c r="Q9" s="116"/>
+      <c r="R9" s="116"/>
+      <c r="S9" s="116"/>
+      <c r="T9" s="116"/>
+      <c r="U9" s="116"/>
+      <c r="V9" s="116"/>
+      <c r="W9" s="116"/>
+      <c r="X9" s="116"/>
+    </row>
+    <row r="10" spans="1:24">
+      <c r="A10" s="127" t="s">
+        <v>6</v>
+      </c>
+      <c r="O10" s="116"/>
+      <c r="P10" s="116"/>
+      <c r="Q10" s="116"/>
+      <c r="R10" s="116"/>
+      <c r="S10" s="116"/>
+      <c r="T10" s="116"/>
+      <c r="U10" s="116"/>
+      <c r="V10" s="116"/>
+      <c r="W10" s="116"/>
+      <c r="X10" s="116"/>
+    </row>
+    <row r="11" spans="1:24">
+      <c r="A11" s="114"/>
+      <c r="O11" s="116"/>
+      <c r="P11" s="116"/>
+      <c r="Q11" s="116"/>
+      <c r="R11" s="116"/>
+      <c r="S11" s="116"/>
+      <c r="T11" s="116"/>
+      <c r="U11" s="116"/>
+      <c r="V11" s="116"/>
+      <c r="W11" s="116"/>
+      <c r="X11" s="116"/>
+    </row>
+    <row r="12" ht="25.5" spans="2:24">
+      <c r="B12" s="118" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="119" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="120" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="36" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="36">
-        <f>COUNTIFS('Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$G:$G,E4)</f>
-        <v>0</v>
-      </c>
-      <c r="F5" s="36">
-        <f>COUNTIFS('Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$G:$G,F4)</f>
-        <v>0</v>
-      </c>
-      <c r="G5" s="36">
-        <f>COUNTIFS('Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$G:$G,G4)</f>
-        <v>0</v>
-      </c>
-      <c r="H5" s="36">
-        <f>COUNTIFS('Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$G:$G,H4)</f>
-        <v>0</v>
-      </c>
-      <c r="I5" s="36">
-        <f>COUNTIFS('Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$G:$G,I4)</f>
-        <v>0</v>
-      </c>
-      <c r="J5" s="36">
-        <f>COUNTIFS('Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$G:$G,J4)</f>
-        <v>0</v>
-      </c>
-      <c r="K5" s="36">
-        <f>COUNTIFS('Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$G:$G,K4)</f>
-        <v>0</v>
-      </c>
-      <c r="L5" s="36">
-        <f>COUNTIFS('Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$G:$G,L4)</f>
-        <v>1</v>
-      </c>
-      <c r="M5" s="36">
-        <f>COUNTIFS('Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$G:$G,M4)</f>
-        <v>0</v>
-      </c>
-      <c r="N5" s="36">
-        <f>COUNTIFS('Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$G:$G,N4)</f>
-        <v>0</v>
-      </c>
-      <c r="O5" s="36">
-        <f>COUNTIFS('Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$G:$G,O4)</f>
-        <v>0</v>
-      </c>
-      <c r="P5" s="36">
-        <f>COUNTIFS('Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$G:$G,P4)</f>
-        <v>0</v>
-      </c>
-      <c r="Q5" s="36">
-        <f>COUNTIFS('Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$G:$G,Q4)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="2:17">
-      <c r="B6" s="37"/>
-      <c r="C6" s="38">
-        <f>COUNTIFS('Ha Noi Progress Tracker'!B:B,B5,'Ha Noi Progress Tracker'!J:J,"&lt;&gt;",'Ha Noi Progress Tracker'!D:D,"&lt;&gt;")</f>
-        <v>3</v>
-      </c>
-      <c r="D6" s="39" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" s="36">
-        <f>COUNTIFS('Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$J:$J,E4)</f>
-        <v>0</v>
-      </c>
-      <c r="F6" s="36">
-        <f>COUNTIFS('Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$J:$J,F4)</f>
-        <v>0</v>
-      </c>
-      <c r="G6" s="36">
-        <f>COUNTIFS('Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$J:$J,G4)</f>
-        <v>0</v>
-      </c>
-      <c r="H6" s="36">
-        <f>COUNTIFS('Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$J:$J,H4)</f>
-        <v>0</v>
-      </c>
-      <c r="I6" s="36">
-        <f>COUNTIFS('Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$J:$J,I4)</f>
-        <v>0</v>
-      </c>
-      <c r="J6" s="36">
-        <f>COUNTIFS('Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$J:$J,J4)</f>
-        <v>0</v>
-      </c>
-      <c r="K6" s="36">
-        <f>COUNTIFS('Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$J:$J,K4)</f>
-        <v>0</v>
-      </c>
-      <c r="L6" s="36">
-        <f>COUNTIFS('Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$J:$J,L4)</f>
-        <v>1</v>
-      </c>
-      <c r="M6" s="36">
-        <f>COUNTIFS('Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$J:$J,M4)</f>
-        <v>0</v>
-      </c>
-      <c r="N6" s="36">
-        <f>COUNTIFS('Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$J:$J,N4)</f>
-        <v>0</v>
-      </c>
-      <c r="O6" s="36">
-        <f>COUNTIFS('Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$J:$J,O4)</f>
-        <v>0</v>
-      </c>
-      <c r="P6" s="36">
-        <f>COUNTIFS('Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$J:$J,P4)</f>
-        <v>0</v>
-      </c>
-      <c r="Q6" s="36">
-        <f>COUNTIFS('Ha Noi Progress Tracker'!$D:$D,"&lt;&gt;",'Ha Noi Progress Tracker'!$B:$B,$B$5,'Ha Noi Progress Tracker'!$J:$J,Q4)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="15:17">
-      <c r="O7" s="29"/>
-      <c r="P7" s="29"/>
-      <c r="Q7" s="29"/>
-    </row>
-    <row r="8" spans="15:17">
-      <c r="O8" s="29"/>
-      <c r="P8" s="29"/>
-      <c r="Q8" s="29"/>
-    </row>
-    <row r="9" spans="15:17">
-      <c r="O9" s="29"/>
-      <c r="P9" s="29"/>
-      <c r="Q9" s="29"/>
-    </row>
-    <row r="10" spans="1:17">
-      <c r="A10" s="40" t="s">
-        <v>6</v>
-      </c>
-      <c r="O10" s="29"/>
-      <c r="P10" s="29"/>
-      <c r="Q10" s="29"/>
-    </row>
-    <row r="11" spans="1:17">
-      <c r="A11" s="27"/>
-      <c r="O11" s="29"/>
-      <c r="P11" s="29"/>
-      <c r="Q11" s="29"/>
-    </row>
-    <row r="12" ht="25.5" spans="2:17">
-      <c r="B12" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="D12" s="33" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12" s="43">
+      <c r="E12" s="130">
         <v>46141</v>
       </c>
-      <c r="F12" s="43">
+      <c r="F12" s="130">
         <f>E12+1</f>
         <v>46142</v>
       </c>
-      <c r="G12" s="43">
-        <f t="shared" ref="G12:Q12" si="1">F12+1</f>
+      <c r="G12" s="130">
+        <f t="shared" ref="G12:X12" si="1">F12+1</f>
         <v>46143</v>
       </c>
-      <c r="H12" s="43">
+      <c r="H12" s="130">
         <f t="shared" si="1"/>
         <v>46144</v>
       </c>
-      <c r="I12" s="43">
+      <c r="I12" s="130">
         <f t="shared" si="1"/>
         <v>46145</v>
       </c>
-      <c r="J12" s="43">
+      <c r="J12" s="130">
         <f t="shared" si="1"/>
         <v>46146</v>
       </c>
-      <c r="K12" s="43">
+      <c r="K12" s="130">
         <f t="shared" si="1"/>
         <v>46147</v>
       </c>
-      <c r="L12" s="43">
+      <c r="L12" s="130">
         <f t="shared" si="1"/>
         <v>46148</v>
       </c>
-      <c r="M12" s="43">
+      <c r="M12" s="130">
         <f t="shared" si="1"/>
         <v>46149</v>
       </c>
-      <c r="N12" s="43">
+      <c r="N12" s="130">
         <f t="shared" si="1"/>
         <v>46150</v>
       </c>
-      <c r="O12" s="43">
+      <c r="O12" s="130">
         <f t="shared" si="1"/>
         <v>46151</v>
       </c>
-      <c r="P12" s="43">
+      <c r="P12" s="130">
         <f t="shared" si="1"/>
         <v>46152</v>
       </c>
-      <c r="Q12" s="43">
+      <c r="Q12" s="130">
         <f t="shared" si="1"/>
         <v>46153</v>
       </c>
-    </row>
-    <row r="13" spans="2:17">
-      <c r="B13" s="41" t="s">
+      <c r="R12" s="130">
+        <f t="shared" si="1"/>
+        <v>46154</v>
+      </c>
+      <c r="S12" s="130">
+        <f t="shared" si="1"/>
+        <v>46155</v>
+      </c>
+      <c r="T12" s="130">
+        <f t="shared" si="1"/>
+        <v>46156</v>
+      </c>
+      <c r="U12" s="130">
+        <f t="shared" si="1"/>
+        <v>46157</v>
+      </c>
+      <c r="V12" s="130">
+        <f t="shared" si="1"/>
+        <v>46158</v>
+      </c>
+      <c r="W12" s="130">
+        <f t="shared" si="1"/>
+        <v>46159</v>
+      </c>
+      <c r="X12" s="130">
+        <f t="shared" si="1"/>
+        <v>46160</v>
+      </c>
+    </row>
+    <row r="13" spans="2:24">
+      <c r="B13" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="38">
-        <f>COUNTIFS('North Progress Tracker'!B:B,B13,'North Progress Tracker'!C:C,"&lt;&gt;")</f>
+      <c r="C13" s="125">
+        <f>COUNTIFS('North Progress Tracker'!B:B,B13,'North Progress Tracker'!J:J,"&lt;&gt;")</f>
         <v>3</v>
       </c>
-      <c r="D13" s="42" t="s">
+      <c r="D13" s="129" t="s">
         <v>5</v>
       </c>
-      <c r="E13" s="36">
-        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$I:$I,E12,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+      <c r="E13" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,E12,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
         <v>1</v>
       </c>
-      <c r="F13" s="36">
-        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$I:$I,F12,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-      <c r="G13" s="36">
-        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$I:$I,G12,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-      <c r="H13" s="36">
-        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$I:$I,H12,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-      <c r="I13" s="36">
-        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$I:$I,I12,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-      <c r="J13" s="36">
-        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$I:$I,J12,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-      <c r="K13" s="36">
-        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$I:$I,K12,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-      <c r="L13" s="36">
-        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$I:$I,L12,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-      <c r="M13" s="36">
-        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$I:$I,M12,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+      <c r="F13" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,F12,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,G12,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,H12,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,I12,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,J12,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,K12,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,L12,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="M13" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,M12,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
         <v>1</v>
       </c>
-      <c r="N13" s="36">
-        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$I:$I,N12,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+      <c r="N13" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,N12,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
         <v>1</v>
       </c>
-      <c r="O13" s="36">
-        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$I:$I,O12,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-      <c r="P13" s="36">
-        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$I:$I,P12,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-      <c r="Q13" s="36">
-        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$I:$I,Q12,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+      <c r="O13" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,O12,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="P13" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,P12,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="Q13" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,Q12,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="R13" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,R12,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="S13" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,S12,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="T13" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,T12,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="U13" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,U12,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="V13" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,V12,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="W13" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,W12,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="X13" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,X12,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:24">
+      <c r="B14" s="123" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="125">
+        <f>COUNTIFS('North Progress Tracker'!B:B,B14,'North Progress Tracker'!J:J,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="129" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,E13,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,F13,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,G13,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,H13,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,I13,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,J13,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,K13,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="L14" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,L13,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="M14" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,M13,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="N14" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,N13,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="O14" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,O13,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="P14" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,P13,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,Q13,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="R14" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,R13,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="S14" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,S13,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="T14" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,T13,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="U14" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,U13,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="V14" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,V13,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="W14" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,W13,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="X14" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,X13,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:24">
+      <c r="B15" s="123" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="125">
+        <f>COUNTIFS('North Progress Tracker'!B:B,B15,'North Progress Tracker'!J:J,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="129" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,E14,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,F14,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,G14,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,H14,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,I14,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="J15" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,J14,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,K14,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="L15" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,L14,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="M15" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,M14,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="N15" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,N14,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="O15" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,O14,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="P15" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,P14,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,Q14,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="R15" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,R14,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="S15" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,S14,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="T15" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,T14,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="U15" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,U14,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="V15" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,V14,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="W15" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,W14,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="X15" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,X14,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:24">
+      <c r="B16" s="123" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="125">
+        <f>COUNTIFS('North Progress Tracker'!B:B,B16,'North Progress Tracker'!J:J,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="129" t="s">
+        <v>5</v>
+      </c>
+      <c r="E16" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,E15,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,F15,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,G15,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,H15,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,I15,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="J16" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,J15,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,K15,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="L16" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,L15,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="M16" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,M15,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="N16" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,N15,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="O16" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,O15,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="P16" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,P15,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,Q15,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="R16" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,R15,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="S16" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,S15,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="T16" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,T15,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="U16" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,U15,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="V16" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,V15,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="W16" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,W15,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="X16" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,X15,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:24">
+      <c r="B17" s="123" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="125">
+        <f>COUNTIFS('North Progress Tracker'!B:B,B17,'North Progress Tracker'!J:J,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="129" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,E16,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,F16,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,G16,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,H16,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,I16,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,J16,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="K17" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,K16,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="L17" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,L16,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="M17" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,M16,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="N17" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,N16,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="O17" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,O16,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="P17" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,P16,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,Q16,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="R17" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,R16,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="S17" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,S16,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="T17" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,T16,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="U17" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,U16,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="V17" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,V16,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="W17" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,W16,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="X17" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,X16,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:24">
+      <c r="B18" s="123" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="125">
+        <f>COUNTIFS('North Progress Tracker'!B:B,B18,'North Progress Tracker'!J:J,"&lt;&gt;")</f>
+        <v>1</v>
+      </c>
+      <c r="D18" s="129" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,E17,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,F17,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,G17,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,H17,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,I17,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,J17,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="K18" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,K17,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="L18" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,L17,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="M18" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,M17,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="N18" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,N17,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="O18" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,O17,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="P18" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,P17,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="Q18" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,Q17,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="R18" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,R17,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="S18" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,S17,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="T18" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,T17,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="U18" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,U17,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="V18" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,V17,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="W18" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,W17,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="X18" s="123">
+        <f>COUNTIFS('North Progress Tracker'!$B:$B,$B$13,'North Progress Tracker'!$J:$J,X17,'North Progress Tracker'!$C:$C,"&lt;&gt;")</f>
         <v>0</v>
       </c>
     </row>
@@ -1726,287 +3092,1525 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:AE37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="3.375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="7.25" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.4416666666667" style="2" customWidth="1"/>
-    <col min="4" max="4" width="25.4166666666667" style="2" customWidth="1"/>
-    <col min="5" max="5" width="11.775" style="2" customWidth="1"/>
-    <col min="6" max="7" width="14.2166666666667" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.2166666666667" style="2" customWidth="1"/>
-    <col min="9" max="10" width="14.2166666666667" style="2" customWidth="1"/>
-    <col min="11" max="11" width="13.2166666666667" style="2" customWidth="1"/>
-    <col min="12" max="12" width="27.3083333333333" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="3.375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="7.25" style="2" customWidth="1"/>
+    <col min="3" max="3" width="6.25" style="3" customWidth="1"/>
+    <col min="4" max="4" width="25.375" style="3" customWidth="1"/>
+    <col min="5" max="6" width="5.50833333333333" style="2" customWidth="1"/>
+    <col min="7" max="7" width="5.50833333333333" style="3" customWidth="1"/>
+    <col min="8" max="8" width="8.875" style="35" customWidth="1"/>
+    <col min="9" max="9" width="8.75" style="35" customWidth="1"/>
+    <col min="10" max="10" width="9.375" style="35" customWidth="1"/>
+    <col min="11" max="11" width="18.0166666666667" style="35" customWidth="1"/>
+    <col min="12" max="12" width="8.875" style="35" customWidth="1"/>
+    <col min="13" max="13" width="8.75" style="35" customWidth="1"/>
+    <col min="14" max="14" width="9.375" style="35" customWidth="1"/>
+    <col min="15" max="15" width="15.025" style="35" customWidth="1"/>
+    <col min="16" max="16" width="8.41666666666667" style="35" customWidth="1"/>
+    <col min="17" max="17" width="9.225" style="35" customWidth="1"/>
+    <col min="18" max="18" width="13.8916666666667" style="35" customWidth="1"/>
+    <col min="19" max="19" width="18.125" style="35" customWidth="1"/>
+    <col min="20" max="20" width="28.375" style="35" customWidth="1"/>
+    <col min="21" max="22" width="13.6" style="2" customWidth="1"/>
+    <col min="23" max="23" width="22.625" style="3" customWidth="1"/>
+    <col min="24" max="24" width="7" style="3" customWidth="1"/>
+    <col min="25" max="25" width="6.5" style="3" customWidth="1"/>
+    <col min="26" max="26" width="158.333333333333" style="3" customWidth="1"/>
+    <col min="27" max="16383" width="9" style="3" customWidth="1"/>
+    <col min="16384" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21.85" customHeight="1" spans="2:12">
-      <c r="B1" s="10"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="12" t="s">
+    <row r="1" ht="21.85" customHeight="1" spans="2:25">
+      <c r="B1" s="36"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="65" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="5"/>
-    </row>
-    <row r="2" ht="23" customHeight="1" spans="1:12">
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="79"/>
+      <c r="P1" s="80"/>
+      <c r="Q1" s="80"/>
+      <c r="R1" s="80"/>
+      <c r="S1" s="80"/>
+      <c r="T1" s="80"/>
+      <c r="U1" s="62" t="s">
+        <v>13</v>
+      </c>
+      <c r="W1" s="2"/>
+      <c r="X1" s="2"/>
+      <c r="Y1" s="2"/>
+    </row>
+    <row r="2" s="2" customFormat="1" ht="39.5" customHeight="1" spans="1:26">
       <c r="A2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="52" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="40" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="54" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="54" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" s="54" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="66" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" s="67" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" s="67" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="O2" s="81" t="s">
+        <v>23</v>
+      </c>
+      <c r="P2" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q2" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="R2" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="S2" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="T2" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="U2" s="104" t="s">
+        <v>29</v>
+      </c>
+      <c r="V2" s="104" t="s">
+        <v>30</v>
+      </c>
+      <c r="W2" s="104" t="s">
+        <v>31</v>
+      </c>
+      <c r="X2" s="104" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y2" s="104" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z2" s="108" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" s="2" customFormat="1" ht="39.5" customHeight="1" spans="1:31">
+      <c r="A3" s="6"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="54"/>
+      <c r="K3" s="68"/>
+      <c r="L3" s="67"/>
+      <c r="M3" s="67"/>
+      <c r="N3" s="67"/>
+      <c r="O3" s="82"/>
+      <c r="P3" s="83"/>
+      <c r="Q3" s="91"/>
+      <c r="R3" s="83"/>
+      <c r="S3" s="83"/>
+      <c r="T3" s="92"/>
+      <c r="U3" s="104"/>
+      <c r="V3" s="104"/>
+      <c r="W3" s="104"/>
+      <c r="X3" s="105"/>
+      <c r="Y3" s="109"/>
+      <c r="Z3" s="4"/>
+      <c r="AC3" s="113"/>
+      <c r="AD3" s="113"/>
+      <c r="AE3" s="113"/>
+    </row>
+    <row r="4" ht="14.25" spans="1:31">
+      <c r="A4" s="4">
+        <v>1</v>
+      </c>
+      <c r="B4" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="43" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="42" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" s="36" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" s="56">
+        <v>46148</v>
+      </c>
+      <c r="I4" s="56">
+        <v>46148</v>
+      </c>
+      <c r="J4" s="69">
+        <v>0.699305555555556</v>
+      </c>
+      <c r="K4" s="70" t="s">
+        <v>40</v>
+      </c>
+      <c r="L4" s="56">
+        <v>46148</v>
+      </c>
+      <c r="M4" s="56">
+        <v>46148</v>
+      </c>
+      <c r="N4" s="69">
+        <v>0.699305555555556</v>
+      </c>
+      <c r="O4" s="84" t="s">
+        <v>40</v>
+      </c>
+      <c r="P4" s="84" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q4" s="47" t="s">
+        <v>41</v>
+      </c>
+      <c r="R4" s="93"/>
+      <c r="S4" s="93"/>
+      <c r="T4" s="94" t="s">
+        <v>42</v>
+      </c>
+      <c r="U4" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="V4" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="W4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="X4" s="106" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y4" s="110" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z4" s="5"/>
+      <c r="AC4" s="113"/>
+      <c r="AD4" s="113"/>
+      <c r="AE4" s="113"/>
+    </row>
+    <row r="5" ht="14.25" spans="1:31">
+      <c r="A5" s="4">
+        <v>2</v>
+      </c>
+      <c r="B5" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="43" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="42" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" s="57">
+        <v>46153</v>
+      </c>
+      <c r="I5" s="57">
+        <v>46153</v>
+      </c>
+      <c r="J5" s="71">
+        <v>0.635416666666667</v>
+      </c>
+      <c r="K5" s="70" t="s">
+        <v>40</v>
+      </c>
+      <c r="L5" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="M5" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="N5" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="O5" s="84" t="s">
+        <v>47</v>
+      </c>
+      <c r="P5" s="84" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q5" s="47" t="s">
+        <v>41</v>
+      </c>
+      <c r="R5" s="44"/>
+      <c r="S5" s="44"/>
+      <c r="T5" s="95" t="s">
+        <v>48</v>
+      </c>
+      <c r="U5" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="V5" s="4"/>
+      <c r="W5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="X5" s="106" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y5" s="110" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z5" s="5"/>
+      <c r="AC5" s="113"/>
+      <c r="AD5" s="113"/>
+      <c r="AE5" s="113"/>
+    </row>
+    <row r="6" ht="14.25" spans="1:31">
+      <c r="A6" s="4">
+        <v>3</v>
+      </c>
+      <c r="B6" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="43" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="57">
+        <v>46153</v>
+      </c>
+      <c r="I6" s="57">
+        <v>46153</v>
+      </c>
+      <c r="J6" s="71">
+        <v>0.753472222222222</v>
+      </c>
+      <c r="K6" s="70" t="s">
+        <v>40</v>
+      </c>
+      <c r="L6" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="M6" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="N6" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="O6" s="84" t="s">
+        <v>47</v>
+      </c>
+      <c r="P6" s="84" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q6" s="47" t="s">
+        <v>41</v>
+      </c>
+      <c r="R6" s="44"/>
+      <c r="S6" s="44"/>
+      <c r="T6" s="95" t="s">
+        <v>48</v>
+      </c>
+      <c r="U6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="V6" s="4"/>
+      <c r="W6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="X6" s="106" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y6" s="110" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z6" s="5"/>
+      <c r="AC6" s="113"/>
+      <c r="AD6" s="113"/>
+      <c r="AE6" s="113"/>
+    </row>
+    <row r="7" ht="14.25" spans="1:31">
+      <c r="A7" s="4">
+        <v>4</v>
+      </c>
+      <c r="B7" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7" s="43" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" s="59">
+        <v>46157</v>
+      </c>
+      <c r="I7" s="20">
+        <v>46157</v>
+      </c>
+      <c r="J7" s="72">
+        <v>0.75</v>
+      </c>
+      <c r="K7" s="70" t="s">
+        <v>40</v>
+      </c>
+      <c r="L7" s="20">
+        <v>46157</v>
+      </c>
+      <c r="M7" s="20">
+        <v>46157</v>
+      </c>
+      <c r="N7" s="72">
+        <v>0.75</v>
+      </c>
+      <c r="O7" s="85" t="s">
+        <v>40</v>
+      </c>
+      <c r="P7" s="47" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q7" s="47" t="s">
+        <v>41</v>
+      </c>
+      <c r="R7" s="96">
+        <v>46157.7847222222</v>
+      </c>
+      <c r="S7" s="97">
+        <v>46157.85</v>
+      </c>
+      <c r="T7" s="98" t="s">
+        <v>55</v>
+      </c>
+      <c r="U7" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="V7" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="W7" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="X7" s="106" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y7" s="110" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z7" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC7" s="113"/>
+      <c r="AD7" s="113"/>
+      <c r="AE7" s="113"/>
+    </row>
+    <row r="8" ht="14.25" spans="1:31">
+      <c r="A8" s="4">
+        <v>5</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8" s="60">
+        <v>46157</v>
+      </c>
+      <c r="I8" s="20">
+        <v>46157</v>
+      </c>
+      <c r="J8" s="72">
+        <v>0.75</v>
+      </c>
+      <c r="K8" s="70" t="s">
+        <v>40</v>
+      </c>
+      <c r="L8" s="20">
+        <v>46157</v>
+      </c>
+      <c r="M8" s="20">
+        <v>46157</v>
+      </c>
+      <c r="N8" s="72">
+        <v>0.75</v>
+      </c>
+      <c r="O8" s="85" t="s">
+        <v>60</v>
+      </c>
+      <c r="P8" s="86" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q8" s="47" t="s">
+        <v>41</v>
+      </c>
+      <c r="R8" s="96">
+        <v>46157.75</v>
+      </c>
+      <c r="S8" s="97">
+        <v>46157.9048611111</v>
+      </c>
+      <c r="T8" s="99" t="s">
+        <v>55</v>
+      </c>
+      <c r="U8" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="V8" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="W8" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="X8" s="106" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y8" s="110" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z8" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="AC8" s="113"/>
+      <c r="AD8" s="113"/>
+      <c r="AE8" s="113"/>
+    </row>
+    <row r="9" ht="14.25" spans="1:31">
+      <c r="A9" s="4">
+        <v>6</v>
+      </c>
+      <c r="B9" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9" s="60">
+        <v>46157</v>
+      </c>
+      <c r="I9" s="20">
+        <v>46157</v>
+      </c>
+      <c r="J9" s="73">
+        <v>0.618055555555556</v>
+      </c>
+      <c r="K9" s="74" t="s">
+        <v>40</v>
+      </c>
+      <c r="L9" s="20">
+        <v>46157</v>
+      </c>
+      <c r="M9" s="20">
+        <v>46157</v>
+      </c>
+      <c r="N9" s="73">
+        <v>0.618055555555556</v>
+      </c>
+      <c r="O9" s="87" t="s">
+        <v>40</v>
+      </c>
+      <c r="P9" s="87" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q9" s="47" t="s">
+        <v>41</v>
+      </c>
+      <c r="R9" s="97" t="s">
+        <v>64</v>
+      </c>
+      <c r="S9" s="97">
+        <v>46157.8916666667</v>
+      </c>
+      <c r="T9" s="99" t="s">
+        <v>55</v>
+      </c>
+      <c r="U9" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="V9" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="W9" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="X9" s="106" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y9" s="110" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z9" s="5"/>
+      <c r="AC9" s="113"/>
+      <c r="AD9" s="113"/>
+      <c r="AE9" s="113"/>
+    </row>
+    <row r="10" ht="14.25" spans="1:31">
+      <c r="A10" s="4">
+        <v>7</v>
+      </c>
+      <c r="B10" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" s="60">
+        <v>46157</v>
+      </c>
+      <c r="I10" s="20">
+        <v>46157</v>
+      </c>
+      <c r="J10" s="73">
+        <v>0.753472222222222</v>
+      </c>
+      <c r="K10" s="74" t="s">
+        <v>40</v>
+      </c>
+      <c r="L10" s="20">
+        <v>46157</v>
+      </c>
+      <c r="M10" s="20">
+        <v>46157</v>
+      </c>
+      <c r="N10" s="73">
+        <v>0.753472222222222</v>
+      </c>
+      <c r="O10" s="85" t="s">
+        <v>60</v>
+      </c>
+      <c r="P10" s="86" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q10" s="47" t="s">
+        <v>41</v>
+      </c>
+      <c r="R10" s="97">
+        <v>46157.7638888889</v>
+      </c>
+      <c r="S10" s="97">
+        <v>46157.8236111111</v>
+      </c>
+      <c r="T10" s="99" t="s">
+        <v>55</v>
+      </c>
+      <c r="U10" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="V10" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="W10" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="X10" s="106" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y10" s="110" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z10" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="AC10" s="113"/>
+      <c r="AD10" s="113"/>
+      <c r="AE10" s="113"/>
+    </row>
+    <row r="11" ht="14.25" spans="1:31">
+      <c r="A11" s="4">
         <v>8</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="8" t="s">
+      <c r="B11" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="G11" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="H11" s="60">
+        <v>46157</v>
+      </c>
+      <c r="I11" s="20">
+        <v>46157</v>
+      </c>
+      <c r="J11" s="73">
+        <v>0.753472222222222</v>
+      </c>
+      <c r="K11" s="73" t="s">
+        <v>60</v>
+      </c>
+      <c r="L11" s="20">
+        <v>46157</v>
+      </c>
+      <c r="M11" s="20">
+        <v>46157</v>
+      </c>
+      <c r="N11" s="73">
+        <v>0.753472222222222</v>
+      </c>
+      <c r="O11" s="85" t="s">
+        <v>60</v>
+      </c>
+      <c r="P11" s="86" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q11" s="47" t="s">
+        <v>41</v>
+      </c>
+      <c r="R11" s="97">
+        <v>46157.85</v>
+      </c>
+      <c r="S11" s="97" t="s">
+        <v>70</v>
+      </c>
+      <c r="T11" s="99" t="s">
+        <v>55</v>
+      </c>
+      <c r="U11" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="V11" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="W11" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="X11" s="106" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y11" s="110" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z11" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC11" s="113"/>
+      <c r="AD11" s="113"/>
+      <c r="AE11" s="113"/>
+    </row>
+    <row r="12" ht="14.25" spans="1:31">
+      <c r="A12" s="4">
         <v>9</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="B12" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="H12" s="60">
+        <v>46157</v>
+      </c>
+      <c r="I12" s="20">
+        <v>46157</v>
+      </c>
+      <c r="J12" s="73">
+        <v>0.756944444444444</v>
+      </c>
+      <c r="K12" s="71" t="s">
+        <v>40</v>
+      </c>
+      <c r="L12" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="M12" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="N12" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="O12" s="87" t="s">
+        <v>74</v>
+      </c>
+      <c r="P12" s="86" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q12" s="47" t="s">
+        <v>41</v>
+      </c>
+      <c r="R12" s="97">
+        <v>46157.7986111111</v>
+      </c>
+      <c r="S12" s="97">
+        <v>46157.85</v>
+      </c>
+      <c r="T12" s="99" t="s">
+        <v>55</v>
+      </c>
+      <c r="U12" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="V12" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="W12" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="X12" s="106" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y12" s="110" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z12" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC12" s="113"/>
+      <c r="AD12" s="113"/>
+      <c r="AE12" s="113"/>
+    </row>
+    <row r="13" ht="14.25" spans="1:31">
+      <c r="A13" s="4">
         <v>10</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="B13" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="G13" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="H13" s="60">
+        <v>46157</v>
+      </c>
+      <c r="I13" s="20">
+        <v>46157</v>
+      </c>
+      <c r="J13" s="73">
+        <v>0.756944444444444</v>
+      </c>
+      <c r="K13" s="73" t="s">
+        <v>60</v>
+      </c>
+      <c r="L13" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="M13" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="N13" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="O13" s="87" t="s">
+        <v>74</v>
+      </c>
+      <c r="P13" s="86" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q13" s="47" t="s">
+        <v>41</v>
+      </c>
+      <c r="R13" s="97">
+        <v>46157.8993055556</v>
+      </c>
+      <c r="S13" s="97" t="s">
+        <v>78</v>
+      </c>
+      <c r="T13" s="99" t="s">
+        <v>55</v>
+      </c>
+      <c r="U13" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="V13" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="W13" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="X13" s="106" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y13" s="110" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z13" s="5"/>
+      <c r="AC13" s="113"/>
+      <c r="AD13" s="113"/>
+      <c r="AE13" s="113"/>
+    </row>
+    <row r="14" ht="14.25" spans="1:31">
+      <c r="A14" s="4">
         <v>11</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="B14" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F14" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="G14" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="H14" s="60">
+        <v>46157</v>
+      </c>
+      <c r="I14" s="20">
+        <v>46157</v>
+      </c>
+      <c r="J14" s="73">
+        <v>0.672222222222222</v>
+      </c>
+      <c r="K14" s="74" t="s">
+        <v>40</v>
+      </c>
+      <c r="L14" s="20">
+        <v>46157</v>
+      </c>
+      <c r="M14" s="20">
+        <v>46157</v>
+      </c>
+      <c r="N14" s="73">
+        <v>0.672222222222222</v>
+      </c>
+      <c r="O14" s="87" t="s">
+        <v>40</v>
+      </c>
+      <c r="P14" s="86" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q14" s="47" t="s">
+        <v>41</v>
+      </c>
+      <c r="R14" s="96">
+        <v>46157.9826388889</v>
+      </c>
+      <c r="S14" s="97">
+        <v>46158.0402777778</v>
+      </c>
+      <c r="T14" s="99" t="s">
+        <v>55</v>
+      </c>
+      <c r="U14" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="V14" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="W14" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="X14" s="106" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y14" s="110" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z14" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC14" s="113"/>
+      <c r="AD14" s="113"/>
+      <c r="AE14" s="113"/>
+    </row>
+    <row r="15" ht="14.25" spans="1:31">
+      <c r="A15" s="4">
         <v>12</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="B15" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F15" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="G15" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="H15" s="60">
+        <v>46157</v>
+      </c>
+      <c r="I15" s="20">
+        <v>46157</v>
+      </c>
+      <c r="J15" s="73">
+        <v>0.672222222222222</v>
+      </c>
+      <c r="K15" s="74" t="s">
+        <v>40</v>
+      </c>
+      <c r="L15" s="20">
+        <v>46157</v>
+      </c>
+      <c r="M15" s="20">
+        <v>46157</v>
+      </c>
+      <c r="N15" s="73">
+        <v>0.672222222222222</v>
+      </c>
+      <c r="O15" s="87" t="s">
+        <v>40</v>
+      </c>
+      <c r="P15" s="87" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q15" s="47" t="s">
+        <v>41</v>
+      </c>
+      <c r="R15" s="97">
+        <v>46157.96875</v>
+      </c>
+      <c r="S15" s="97">
+        <v>46157.9965277778</v>
+      </c>
+      <c r="T15" s="99" t="s">
+        <v>55</v>
+      </c>
+      <c r="U15" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="V15" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="W15" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="X15" s="106" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y15" s="110" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z15" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC15" s="113"/>
+      <c r="AD15" s="113"/>
+      <c r="AE15" s="113"/>
+    </row>
+    <row r="16" ht="14.25" spans="1:31">
+      <c r="A16" s="4">
         <v>13</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="B16" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="C16" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F16" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="H16" s="60">
+        <v>46157</v>
+      </c>
+      <c r="I16" s="20">
+        <v>46157</v>
+      </c>
+      <c r="J16" s="73">
+        <v>0.645833333333333</v>
+      </c>
+      <c r="K16" s="74" t="s">
+        <v>40</v>
+      </c>
+      <c r="L16" s="20">
+        <v>46157</v>
+      </c>
+      <c r="M16" s="20">
+        <v>46157</v>
+      </c>
+      <c r="N16" s="73">
+        <v>0.645833333333333</v>
+      </c>
+      <c r="O16" s="87" t="s">
+        <v>40</v>
+      </c>
+      <c r="P16" s="86" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q16" s="47" t="s">
+        <v>41</v>
+      </c>
+      <c r="R16" s="97">
+        <v>46157.7083333333</v>
+      </c>
+      <c r="S16" s="97">
+        <v>46157.9513888889</v>
+      </c>
+      <c r="T16" s="99" t="s">
+        <v>55</v>
+      </c>
+      <c r="U16" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="V16" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="W16" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="X16" s="106" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y16" s="110" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z16" s="5"/>
+      <c r="AC16" s="113"/>
+      <c r="AD16" s="113"/>
+      <c r="AE16" s="113"/>
+    </row>
+    <row r="17" spans="1:26">
+      <c r="A17" s="45">
         <v>14</v>
       </c>
-      <c r="I2" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="8" t="s">
+      <c r="B17" s="46" t="s">
+        <v>0</v>
+      </c>
+      <c r="C17" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F17" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="G17" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="H17" s="61">
+        <v>46157</v>
+      </c>
+      <c r="I17" s="20">
+        <v>46157</v>
+      </c>
+      <c r="J17" s="75">
+        <v>0.756944444444444</v>
+      </c>
+      <c r="K17" s="70" t="s">
+        <v>40</v>
+      </c>
+      <c r="L17" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="M17" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="N17" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="O17" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="P17" s="88" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q17" s="47" t="s">
+        <v>41</v>
+      </c>
+      <c r="R17" s="97">
+        <v>46157.9166666667</v>
+      </c>
+      <c r="S17" s="88" t="s">
+        <v>89</v>
+      </c>
+      <c r="T17" s="100" t="s">
+        <v>55</v>
+      </c>
+      <c r="U17" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="V17" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="W17" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="X17" s="106" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y17" s="110" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z17" s="9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26">
+      <c r="A18" s="45">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="3">
-        <v>1</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="B18" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="C18" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" s="49" t="s">
+        <v>92</v>
+      </c>
+      <c r="E18" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="F18" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="G18" s="48" t="s">
+        <v>39</v>
+      </c>
+      <c r="H18" s="61">
+        <v>46157</v>
+      </c>
+      <c r="I18" s="76">
+        <v>46157</v>
+      </c>
+      <c r="J18" s="75">
+        <v>0.759027777777778</v>
+      </c>
+      <c r="K18" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="L18" s="76">
+        <v>46157</v>
+      </c>
+      <c r="M18" s="76">
+        <v>46157</v>
+      </c>
+      <c r="N18" s="75">
+        <v>0.759027777777778</v>
+      </c>
+      <c r="O18" s="89" t="s">
+        <v>40</v>
+      </c>
+      <c r="P18" s="88" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q18" s="47" t="s">
+        <v>41</v>
+      </c>
+      <c r="R18" s="101">
+        <v>46157.8465277778</v>
+      </c>
+      <c r="S18" s="88" t="s">
+        <v>93</v>
+      </c>
+      <c r="T18" s="100" t="s">
+        <v>55</v>
+      </c>
+      <c r="U18" s="45" t="s">
+        <v>94</v>
+      </c>
+      <c r="V18" s="45" t="s">
+        <v>94</v>
+      </c>
+      <c r="W18" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="X18" s="106" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y18" s="111" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z18" s="9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26">
+      <c r="A19" s="4">
         <v>16</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="16">
-        <v>46148</v>
-      </c>
-      <c r="G3" s="16">
-        <v>46148</v>
-      </c>
-      <c r="H3" s="17">
-        <v>0.699305555555556</v>
-      </c>
-      <c r="I3" s="16">
-        <v>46148</v>
-      </c>
-      <c r="J3" s="16">
-        <v>46148</v>
-      </c>
-      <c r="K3" s="17">
-        <v>0.699305555555556</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="M3" s="11"/>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="3">
-        <v>2</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" s="25">
-        <v>46153</v>
-      </c>
-      <c r="G4" s="25">
-        <v>46153</v>
-      </c>
-      <c r="H4" s="26">
-        <v>0.635416666666667</v>
-      </c>
-      <c r="I4" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="J4" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="K4" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="L4" s="18" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="3">
-        <v>3</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="25">
-        <v>46153</v>
-      </c>
-      <c r="G5" s="25">
-        <v>46153</v>
-      </c>
-      <c r="H5" s="26">
-        <v>0.753472222222222</v>
-      </c>
-      <c r="I5" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="J5" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="K5" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="L5" s="18" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="3"/>
-      <c r="B6" s="22"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="3"/>
-      <c r="B7" s="22"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="3"/>
-      <c r="B8" s="22"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="3"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="3"/>
-      <c r="B10" s="22"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" s="3"/>
-      <c r="B11" s="22"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-    </row>
-    <row r="17" ht="13.5" spans="9:9">
-      <c r="I17" s="24"/>
-    </row>
-    <row r="20" ht="13.5" spans="4:4">
-      <c r="D20" s="24"/>
+      <c r="B19" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="C19" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F19" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="G19" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="H19" s="60">
+        <v>46157</v>
+      </c>
+      <c r="I19" s="20">
+        <v>46157</v>
+      </c>
+      <c r="J19" s="73">
+        <v>0.759027777777778</v>
+      </c>
+      <c r="K19" s="74" t="s">
+        <v>40</v>
+      </c>
+      <c r="L19" s="20">
+        <v>46157</v>
+      </c>
+      <c r="M19" s="20">
+        <v>46157</v>
+      </c>
+      <c r="N19" s="73">
+        <v>0.759027777777778</v>
+      </c>
+      <c r="O19" s="74" t="s">
+        <v>40</v>
+      </c>
+      <c r="P19" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q19" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="R19" s="102">
+        <v>46157.7916666667</v>
+      </c>
+      <c r="S19" s="102">
+        <v>46157.8465277778</v>
+      </c>
+      <c r="T19" s="103" t="s">
+        <v>96</v>
+      </c>
+      <c r="U19" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="V19" s="4"/>
+      <c r="W19" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="X19" s="106" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y19" s="112" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z19" s="9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="20" spans="13:13">
+      <c r="M20" s="90"/>
+    </row>
+    <row r="22" spans="4:7">
+      <c r="D22" s="50"/>
+      <c r="E22" s="62"/>
+      <c r="F22" s="62"/>
+      <c r="G22" s="50"/>
+    </row>
+    <row r="23" spans="5:5">
+      <c r="E23" s="62"/>
+    </row>
+    <row r="26" ht="14.25" spans="21:21">
+      <c r="U26" s="107"/>
+    </row>
+    <row r="27" ht="14.25" spans="21:21">
+      <c r="U27" s="107"/>
+    </row>
+    <row r="28" ht="14.25" spans="21:21">
+      <c r="U28" s="107"/>
+    </row>
+    <row r="29" ht="14.25" spans="21:21">
+      <c r="U29" s="107"/>
+    </row>
+    <row r="30" ht="14.25" spans="21:21">
+      <c r="U30" s="107"/>
+    </row>
+    <row r="31" ht="14.25" spans="21:21">
+      <c r="U31" s="107"/>
+    </row>
+    <row r="32" ht="14.25" spans="21:21">
+      <c r="U32" s="107"/>
+    </row>
+    <row r="33" ht="14.25" spans="21:21">
+      <c r="U33" s="107"/>
+    </row>
+    <row r="34" ht="14.25" spans="21:21">
+      <c r="U34" s="107"/>
+    </row>
+    <row r="35" ht="14.25" spans="21:21">
+      <c r="U35" s="107"/>
+    </row>
+    <row r="36" ht="14.25" spans="21:21">
+      <c r="U36" s="107"/>
+    </row>
+    <row r="37" ht="14.25" spans="21:21">
+      <c r="U37" s="107"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" insertHyperlinks="0" autoFilter="0"/>
-  <mergeCells count="2">
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:AE19" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
+  <mergeCells count="3">
+    <mergeCell ref="H1:K1"/>
+    <mergeCell ref="L1:O1"/>
+    <mergeCell ref="U1:Y1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -2016,230 +4620,708 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:U17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="10" style="2" customWidth="1"/>
-    <col min="3" max="3" width="26.375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="9.775" style="2" customWidth="1"/>
-    <col min="5" max="5" width="10.3333333333333" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9.88333333333333" style="2" customWidth="1"/>
-    <col min="7" max="7" width="10.775" style="2" customWidth="1"/>
-    <col min="8" max="8" width="10.3333333333333" style="2" customWidth="1"/>
-    <col min="9" max="9" width="9.88333333333333" style="2" customWidth="1"/>
-    <col min="10" max="10" width="10.775" style="2" customWidth="1"/>
-    <col min="11" max="11" width="33.875" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="3.375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="9.75" style="3" customWidth="1"/>
+    <col min="3" max="3" width="26.375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="9.85833333333333" style="3" customWidth="1"/>
+    <col min="5" max="5" width="8.625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="8.875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="8.5" style="3" customWidth="1"/>
+    <col min="8" max="8" width="9.375" style="3" customWidth="1"/>
+    <col min="9" max="9" width="8.875" style="3" customWidth="1"/>
+    <col min="10" max="10" width="8.75" style="3" customWidth="1"/>
+    <col min="11" max="11" width="9.375" style="3" customWidth="1"/>
+    <col min="12" max="12" width="13.625" style="3" customWidth="1"/>
+    <col min="13" max="13" width="16.125" style="3" customWidth="1"/>
+    <col min="14" max="14" width="12.25" style="3" customWidth="1"/>
+    <col min="15" max="15" width="15.625" style="3" customWidth="1"/>
+    <col min="16" max="16" width="28.5" style="3" customWidth="1"/>
+    <col min="17" max="17" width="11.5" style="3" customWidth="1"/>
+    <col min="18" max="18" width="25.625" style="3" customWidth="1"/>
+    <col min="19" max="19" width="6.125" style="3" customWidth="1"/>
+    <col min="20" max="20" width="6.5" style="3" customWidth="1"/>
+    <col min="21" max="21" width="53.5083333333333" style="3" customWidth="1"/>
+    <col min="22" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.35" customHeight="1" spans="1:11">
-      <c r="A1" s="3"/>
-      <c r="B1" s="4"/>
+    <row r="1" ht="19.35" customHeight="1" spans="1:20">
+      <c r="A1" s="4"/>
+      <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
-      <c r="E1" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="5"/>
-    </row>
-    <row r="2" ht="20.1" customHeight="1" spans="1:11">
+      <c r="E1" s="5"/>
+      <c r="F1" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="R1" s="23"/>
+      <c r="S1" s="23"/>
+      <c r="T1" s="24"/>
+    </row>
+    <row r="2" ht="20.1" customHeight="1" spans="1:21">
       <c r="A2" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="3">
+      <c r="C2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="O2" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q2" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="R2" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="S2" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="T2" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="U2" s="34" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20">
+      <c r="A3" s="4">
         <v>1</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="16">
+      <c r="C3" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="8"/>
+      <c r="E3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="13">
         <v>46141</v>
       </c>
-      <c r="I3" s="16">
+      <c r="J3" s="13">
         <v>46141</v>
       </c>
-      <c r="J3" s="17">
+      <c r="K3" s="14">
         <v>0.791666666666667</v>
       </c>
-      <c r="K3" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="3">
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="14"/>
+      <c r="P3" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q3" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="S3" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="T3" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21">
+      <c r="A4" s="4">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="5"/>
+        <v>107</v>
+      </c>
+      <c r="D4" s="5"/>
+      <c r="E4" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
-      <c r="H4" s="16">
+      <c r="H4" s="5"/>
+      <c r="I4" s="13">
         <v>46149</v>
       </c>
-      <c r="I4" s="16">
+      <c r="J4" s="13">
         <v>46149</v>
       </c>
-      <c r="J4" s="17">
+      <c r="K4" s="14">
         <v>0.659722222222222</v>
       </c>
-      <c r="K4" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="3">
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="14"/>
+      <c r="P4" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q4" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="R4" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="S4" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="T4" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="U4" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20">
+      <c r="A5" s="4">
         <v>3</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="5"/>
+        <v>111</v>
+      </c>
+      <c r="D5" s="5"/>
+      <c r="E5" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
-      <c r="H5" s="16">
+      <c r="H5" s="5"/>
+      <c r="I5" s="13">
         <v>46149</v>
       </c>
-      <c r="I5" s="16">
+      <c r="J5" s="13">
         <v>46150</v>
       </c>
-      <c r="J5" s="17">
+      <c r="K5" s="14">
         <v>0.395833333333333</v>
       </c>
-      <c r="K5" s="18" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" s="3"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="5"/>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" s="3"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="5"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="14"/>
+      <c r="N5" s="14"/>
+      <c r="O5" s="14"/>
+      <c r="P5" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q5" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="R5" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="S5" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="T5" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20">
+      <c r="A6" s="4">
+        <v>4</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="D6" s="5"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="J6" s="13"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
+      <c r="N6" s="14"/>
+      <c r="O6" s="14"/>
+      <c r="P6" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q6" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="R6" s="33" t="s">
+        <v>117</v>
+      </c>
+      <c r="S6" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="T6" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20">
+      <c r="A7" s="4">
+        <v>5</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>118</v>
+      </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
+      <c r="I7" s="20">
+        <v>46160</v>
+      </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" s="3"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="5"/>
+      <c r="R7" s="5"/>
+      <c r="S7" s="5"/>
+      <c r="T7" s="5"/>
+    </row>
+    <row r="8" spans="1:20">
+      <c r="A8" s="4">
+        <v>6</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>119</v>
+      </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
+      <c r="I8" s="20">
+        <v>46160</v>
+      </c>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" s="3"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="5"/>
+      <c r="S8" s="5"/>
+      <c r="T8" s="5"/>
+    </row>
+    <row r="9" spans="1:20">
+      <c r="A9" s="4">
+        <v>7</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>120</v>
+      </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
+      <c r="I9" s="20">
+        <v>46160</v>
+      </c>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
-    </row>
-    <row r="17" spans="3:3">
-      <c r="C17" s="11"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5"/>
+      <c r="R9" s="5"/>
+      <c r="S9" s="5"/>
+      <c r="T9" s="5"/>
+    </row>
+    <row r="10" spans="1:20">
+      <c r="A10" s="4">
+        <v>8</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="20">
+        <v>46160</v>
+      </c>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="5"/>
+      <c r="R10" s="5"/>
+      <c r="S10" s="5"/>
+      <c r="T10" s="5"/>
+    </row>
+    <row r="11" spans="1:20">
+      <c r="A11" s="4">
+        <v>9</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="20">
+        <v>46160</v>
+      </c>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="5"/>
+      <c r="S11" s="5"/>
+      <c r="T11" s="5"/>
+    </row>
+    <row r="12" spans="1:20">
+      <c r="A12" s="4">
+        <v>10</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="20">
+        <v>46160</v>
+      </c>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="5"/>
+      <c r="R12" s="5"/>
+      <c r="S12" s="5"/>
+      <c r="T12" s="5"/>
+    </row>
+    <row r="13" spans="1:20">
+      <c r="A13" s="4">
+        <v>11</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="20">
+        <v>46160</v>
+      </c>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="5"/>
+      <c r="R13" s="5"/>
+      <c r="S13" s="5"/>
+      <c r="T13" s="5"/>
+    </row>
+    <row r="14" spans="1:20">
+      <c r="A14" s="4">
+        <v>12</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="20">
+        <v>46160</v>
+      </c>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="5"/>
+      <c r="R14" s="5"/>
+      <c r="S14" s="5"/>
+      <c r="T14" s="5"/>
+    </row>
+    <row r="15" spans="1:20">
+      <c r="A15" s="4">
+        <v>13</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="20">
+        <v>46160</v>
+      </c>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="5"/>
+      <c r="R15" s="5"/>
+      <c r="S15" s="5"/>
+      <c r="T15" s="5"/>
+    </row>
+    <row r="16" spans="1:20">
+      <c r="A16" s="4">
+        <v>14</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="20">
+        <v>46160</v>
+      </c>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="5"/>
+      <c r="R16" s="5"/>
+      <c r="S16" s="5"/>
+      <c r="T16" s="5"/>
+    </row>
+    <row r="17" spans="1:20">
+      <c r="A17" s="4">
+        <v>15</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D17" s="9"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="20">
+        <v>46160</v>
+      </c>
+      <c r="J17" s="20">
+        <v>46160</v>
+      </c>
+      <c r="K17" s="21">
+        <v>0.692361111111111</v>
+      </c>
+      <c r="L17" s="5"/>
+      <c r="M17" s="5"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="5"/>
+      <c r="Q17" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="R17" s="5"/>
+      <c r="S17" s="5"/>
+      <c r="T17" s="5"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" insertHyperlinks="0" autoFilter="0"/>
-  <mergeCells count="2">
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="H1:J1"/>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A2:T17" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
+  <mergeCells count="3">
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="Q1:T1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="2"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1"/>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="1"/>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1"/>
+    </row>
+  </sheetData>
+  <sheetProtection formatCells="0" insertHyperlinks="0" autoFilter="0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetData/>
+  <sheetProtection formatCells="0" insertHyperlinks="0" autoFilter="0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<autofilters xmlns="https://web.wps.cn/et/2018/main"/>
+<autofilters xmlns="https://web.wps.cn/et/2018/main">
+  <sheetItem sheetStid="1">
+    <filterData filterID="AK20210901JXNSXO5332669"/>
+    <autofilterInfo filterID="AK20210901JXNSXO5332669">
+      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A3:AD19"/>
+    </autofilterInfo>
+  </sheetItem>
+  <sheetItem sheetStid="2">
+    <filterData filterID="AK20210901JXNSXO19988694"/>
+    <autofilterInfo filterID="AK20210901JXNSXO19988694">
+      <autoFilter xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A2:S17"/>
+    </autofilterInfo>
+  </sheetItem>
+</autofilters>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2257,6 +5339,10 @@
       <cellprotection/>
       <appEtDbRelations/>
     </woSheetProps>
+    <woSheetProps sheetStid="6" interlineOnOff="0" interlineColor="0" isDbSheet="0" isDashBoardSheet="0" isDbDashBoardSheet="0" isFlexPaperSheet="0">
+      <cellprotection/>
+      <appEtDbRelations/>
+    </woSheetProps>
   </woSheetsProps>
   <woBookProps>
     <bookSettings isFilterShared="0" coreConquerUserId="" isAutoUpdatePaused="0" filterType="user" isMergeTasksAutoUpdate="0" isInserPicAsAttachment="0"/>
@@ -2269,6 +5355,7 @@
   <pixelatorList sheetStid="4"/>
   <pixelatorList sheetStid="1"/>
   <pixelatorList sheetStid="2"/>
+  <pixelatorList sheetStid="6"/>
   <pixelatorList sheetStid="5"/>
 </pixelators>
 </file>

--- a/On Air Progress Tracker.xlsx
+++ b/On Air Progress Tracker.xlsx
@@ -7955,14 +7955,22 @@
         </is>
       </c>
       <c r="D16" s="17" t="n"/>
-      <c r="E16" s="17" t="n"/>
+      <c r="E16" s="17" t="inlineStr">
+        <is>
+          <t>On Air</t>
+        </is>
+      </c>
       <c r="F16" s="17" t="n"/>
-      <c r="G16" s="17" t="n"/>
+      <c r="G16" s="182" t="n">
+        <v>46162</v>
+      </c>
       <c r="H16" s="17" t="n"/>
       <c r="I16" s="20" t="n">
         <v>46160</v>
       </c>
-      <c r="J16" s="17" t="n"/>
+      <c r="J16" s="182" t="n">
+        <v>46162</v>
+      </c>
       <c r="K16" s="17" t="n"/>
       <c r="L16" s="17" t="n"/>
       <c r="M16" s="17" t="n"/>
@@ -8647,7 +8655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U17"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="12.75"/>
   <cols>
     <col width="3.375" customWidth="1" style="67" min="1" max="1"/>
@@ -8826,6 +8834,11 @@
           <t>Alarm（update on May 18 15:00)</t>
         </is>
       </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>RFI Date</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="98" t="n">
@@ -8852,7 +8865,9 @@
         </is>
       </c>
       <c r="F3" s="13" t="n"/>
-      <c r="G3" s="13" t="n"/>
+      <c r="G3" s="13" t="n">
+        <v>46158</v>
+      </c>
       <c r="H3" s="14" t="n"/>
       <c r="I3" s="183" t="n">
         <v>46168</v>
@@ -8884,6 +8899,9 @@
           <t>HUA</t>
         </is>
       </c>
+      <c r="V3" s="177" t="n">
+        <v>46140</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="98" t="n">
@@ -8910,7 +8928,9 @@
         </is>
       </c>
       <c r="F4" s="17" t="n"/>
-      <c r="G4" s="17" t="n"/>
+      <c r="G4" s="182" t="n">
+        <v>46158</v>
+      </c>
       <c r="H4" s="17" t="n"/>
       <c r="I4" s="186" t="n">
         <v>46168</v>
@@ -8941,6 +8961,9 @@
         <is>
           <t>HUA</t>
         </is>
+      </c>
+      <c r="V4" s="177" t="n">
+        <v>46140</v>
       </c>
     </row>
     <row r="5">
@@ -9078,7 +9101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z16"/>
+  <dimension ref="A1:AA16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="12.75"/>
   <cols>
     <col width="3.375" customWidth="1" style="67" min="1" max="1"/>
@@ -9273,6 +9296,11 @@
           <t>Alarm</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>RFI Date</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="78" t="n">
@@ -10110,7 +10138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U7"/>
+  <dimension ref="A1:V7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="12.75" outlineLevelRow="6"/>
   <cols>
     <col width="3.375" customWidth="1" style="67" min="1" max="1"/>
@@ -10277,6 +10305,11 @@
           <t>Alarm（update on May 18 15:00)</t>
         </is>
       </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>RFI Date</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="98" t="n">
